--- a/rtss-pre1917/src/main/resources/census-1897/categories.xlsx
+++ b/rtss-pre1917/src/main/resources/census-1897/categories.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\census-1897\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07331E5-7F71-46F7-8AC8-508E8DDA9536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB10432-CB34-490C-8D7D-D6872C8D7B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="81870" yWindow="3435" windowWidth="28185" windowHeight="19845" activeTab="1" xr2:uid="{92724D0E-B234-4E55-96E7-565027639B5C}"/>
+    <workbookView xWindow="60510" yWindow="1680" windowWidth="24075" windowHeight="17400" activeTab="1" xr2:uid="{92724D0E-B234-4E55-96E7-565027639B5C}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="data" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="163">
   <si>
     <t>губ</t>
   </si>
@@ -382,6 +382,151 @@
   </si>
   <si>
     <t>Ферганская обл.</t>
+  </si>
+  <si>
+    <t>Московская с Москвой</t>
+  </si>
+  <si>
+    <t>Санкт-Петербургская с Санкт-Петербургом</t>
+  </si>
+  <si>
+    <t>Варшавская с Варшавой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Херсонская с Одессой  </t>
+  </si>
+  <si>
+    <t>Таврическая с Севастополем</t>
+  </si>
+  <si>
+    <t>Бакинская с Баку</t>
+  </si>
+  <si>
+    <t>Приморская обл. с Камчатской обл.</t>
+  </si>
+  <si>
+    <t>Кутаисская с Батумской</t>
+  </si>
+  <si>
+    <t>Люблинская с Седлецкой и Холмской</t>
+  </si>
+  <si>
+    <t>примечание</t>
+  </si>
+  <si>
+    <t>В печатном варианте таблиц строки Московская, Санкт-Петербургская, Варшавская и Херсонская уже включают соответствующие города.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это видно из самого устройства «Общего свода». В основной таблице населения губерния даётся целиком, а следующей строкой город помечен как «въ т. ч.»: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Московская — въ т. ч. г. Москва», «С.-Петербургская — въ т. ч. г. С.-Петербург», «Херсонская — въ т. ч. г. Одесса». </t>
+  </si>
+  <si>
+    <t xml:space="preserve">То есть город является частью предыдущего губернского итога, а не исключён из него. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">В приложениях с процентными категориями используется та же территориальная логика: например, в таблице №40 идут «Московская 0,36» и отдельной вложенной строкой «г. Москва 0,77»; </t>
+  </si>
+  <si>
+    <t>аналогично для Петербурга, Одессы и Варшавы. То есть 0,36% — это доля иудеев во всей Московской губернии вместе с Москвой, а 0,77% — отдельно в Москве.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это хорошо проверяется арифметически. Если считать губернские проценты включающими город, то из данных categories.xlsx и census-1897.xlsx </t>
+  </si>
+  <si>
+    <t>получаются вполне естественные показатели для оставшейся части губернии:</t>
+  </si>
+  <si>
+    <t>территория без выделенного города</t>
+  </si>
+  <si>
+    <t>Московская без Москвы</t>
+  </si>
+  <si>
+    <t>≈99,52</t>
+  </si>
+  <si>
+    <t>≈0,19</t>
+  </si>
+  <si>
+    <t>≈0,13</t>
+  </si>
+  <si>
+    <t>≈0,05</t>
+  </si>
+  <si>
+    <t>Санкт-Петербургская без Петербурга</t>
+  </si>
+  <si>
+    <t>≈80,62</t>
+  </si>
+  <si>
+    <t>≈1,40</t>
+  </si>
+  <si>
+    <t>≈19,89</t>
+  </si>
+  <si>
+    <t>≈0,49</t>
+  </si>
+  <si>
+    <t>Варшавская без Варшавы</t>
+  </si>
+  <si>
+    <t>≈3,80</t>
+  </si>
+  <si>
+    <t>≈79,62</t>
+  </si>
+  <si>
+    <t>≈5,68</t>
+  </si>
+  <si>
+    <t>≈10,65</t>
+  </si>
+  <si>
+    <t>Херсонская без Одессы</t>
+  </si>
+  <si>
+    <t>≈78,28</t>
+  </si>
+  <si>
+    <t>≈3,05</t>
+  </si>
+  <si>
+    <t>≈2,71</t>
+  </si>
+  <si>
+    <t>≈8,63</t>
+  </si>
+  <si>
+    <t>строки ниже расчитаны из верхних</t>
+  </si>
+  <si>
+    <t>%
+иудеев</t>
+  </si>
+  <si>
+    <t>Батумская</t>
+  </si>
+  <si>
+    <t>Камчатская обл.</t>
+  </si>
+  <si>
+    <t>взято по Кутаисской</t>
+  </si>
+  <si>
+    <t>взято по Приморской обл.</t>
+  </si>
+  <si>
+    <t>взвешенное усреднение</t>
+  </si>
+  <si>
+    <t>взято по Таврической с Севастополем</t>
+  </si>
+  <si>
+    <t>взято по Бакинской с Баку</t>
   </si>
 </sst>
 </file>
@@ -391,7 +536,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,8 +552,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,6 +569,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,12 +591,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,9 +634,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -498,7 +674,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -604,7 +780,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -746,7 +922,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -754,11 +930,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAD0A7B-3404-42E8-85F9-D8FBA00428FE}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.578125" customWidth="1"/>
+    <col min="2" max="2" width="15.05078125" customWidth="1"/>
     <col min="4" max="4" width="10.578125" customWidth="1"/>
+    <col min="5" max="5" width="12.26171875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -770,7 +948,7 @@
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C3" t="s">
@@ -784,7 +962,7 @@
       <c r="A4" t="s">
         <v>102</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C4" t="s">
@@ -798,7 +976,7 @@
       <c r="A5" t="s">
         <v>106</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C5" t="s">
@@ -812,11 +990,139 @@
       <c r="A6" t="s">
         <v>109</v>
       </c>
+      <c r="B6" s="11" t="s">
+        <v>105</v>
+      </c>
       <c r="C6" t="s">
         <v>111</v>
       </c>
       <c r="E6" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -826,17 +1132,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAED65A-5A6E-43F7-B50C-6E37F76F3A03}">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.41796875" customWidth="1"/>
     <col min="2" max="2" width="9.15625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.15625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.47265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -852,8 +1159,11 @@
       <c r="E1" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G1" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -870,7 +1180,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -887,7 +1197,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -904,7 +1214,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -921,7 +1231,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -938,7 +1248,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -955,7 +1265,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -972,7 +1282,7 @@
         <v>11.79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -989,7 +1299,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1006,7 +1316,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1023,7 +1333,7 @@
         <v>13.24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1040,7 +1350,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1057,7 +1367,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1074,7 +1384,7 @@
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>91</v>
       </c>
@@ -1091,7 +1401,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1280,7 +1590,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="B27" s="2">
         <v>97.8</v>
@@ -1518,7 +1828,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="B41" s="2">
         <v>84.5</v>
@@ -1603,7 +1913,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2">
         <v>70.8</v>
@@ -1705,7 +2015,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="B52" s="2">
         <v>75.400000000000006</v>
@@ -1807,7 +2117,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2">
         <v>5.5</v>
@@ -2011,7 +2321,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="B70" s="2">
         <v>9.4</v>
@@ -2468,7 +2778,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2485,7 +2795,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2502,7 +2812,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2519,7 +2829,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -2534,9 +2844,245 @@
       </c>
       <c r="E100" s="3">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="G102" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" s="10">
+        <v>99.52</v>
+      </c>
+      <c r="C104" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="D104" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="E104" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" t="s">
+        <v>41</v>
+      </c>
+      <c r="B105" s="10">
+        <v>80.62</v>
+      </c>
+      <c r="C105" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="D105" s="10">
+        <v>19.89</v>
+      </c>
+      <c r="E105" s="10">
+        <v>0.49</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" t="s">
+        <v>58</v>
+      </c>
+      <c r="B106" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="C106" s="10">
+        <v>79.62</v>
+      </c>
+      <c r="D106" s="10">
+        <v>5.68</v>
+      </c>
+      <c r="E106" s="10">
+        <v>10.65</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>52</v>
+      </c>
+      <c r="B107" s="10">
+        <v>78.28</v>
+      </c>
+      <c r="C107" s="10">
+        <v>3.05</v>
+      </c>
+      <c r="D107" s="10">
+        <v>2.71</v>
+      </c>
+      <c r="E107" s="10">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" s="2">
+        <v>70.8</v>
+      </c>
+      <c r="C108" s="3">
+        <v>2.11</v>
+      </c>
+      <c r="D108" s="3">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="E108" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>70</v>
+      </c>
+      <c r="B109" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="C109" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D109" s="3">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E109" s="3">
+        <v>1.54</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>121</v>
+      </c>
+      <c r="B111" s="2">
+        <v>50.9</v>
+      </c>
+      <c r="C111" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="D111" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="E111" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="G111" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C112" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="D112" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="E112" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="G112" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" s="10">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="C113" s="10">
+        <v>64.34</v>
+      </c>
+      <c r="D113" s="10">
+        <v>2.13</v>
+      </c>
+      <c r="E113" s="10">
+        <v>14.35</v>
+      </c>
+      <c r="G113" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>156</v>
+      </c>
+      <c r="B115" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C115" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="D115" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="E115" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="G115" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>157</v>
+      </c>
+      <c r="B116" s="2">
+        <v>50.9</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="D116" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="E116" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="G116" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-pre1917/src/main/resources/census-1897/categories.xlsx
+++ b/rtss-pre1917/src/main/resources/census-1897/categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\census-1897\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB10432-CB34-490C-8D7D-D6872C8D7B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD2D356-6F7D-46BE-9F77-5F4C81271907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60510" yWindow="1680" windowWidth="24075" windowHeight="17400" activeTab="1" xr2:uid="{92724D0E-B234-4E55-96E7-565027639B5C}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{92724D0E-B234-4E55-96E7-565027639B5C}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="165">
   <si>
     <t>губ</t>
   </si>
@@ -527,6 +527,12 @@
   </si>
   <si>
     <t>взято по Бакинской с Баку</t>
+  </si>
+  <si>
+    <t>% поляков</t>
+  </si>
+  <si>
+    <t>% поляков из файла poles.xslx</t>
   </si>
 </sst>
 </file>
@@ -930,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAD0A7B-3404-42E8-85F9-D8FBA00428FE}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.578125" customWidth="1"/>
@@ -1057,7 +1063,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="8" t="s">
         <v>134</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="8" t="s">
         <v>139</v>
       </c>
@@ -1091,7 +1097,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="8" t="s">
         <v>144</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="8" t="s">
         <v>149</v>
       </c>
@@ -1123,6 +1129,11 @@
       </c>
       <c r="F25" s="7" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAED65A-5A6E-43F7-B50C-6E37F76F3A03}">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="42.41796875" customWidth="1"/>
@@ -1140,10 +1151,12 @@
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.15625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="49" customWidth="1"/>
+    <col min="6" max="6" width="9.9453125" customWidth="1"/>
+    <col min="8" max="8" width="49" customWidth="1"/>
+    <col min="10" max="10" width="8.83984375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1159,11 +1172,14 @@
       <c r="E1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1179,8 +1195,11 @@
       <c r="E2" s="3">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F2" s="3">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1196,8 +1215,11 @@
       <c r="E3" s="3">
         <v>4.0599999999999996</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F3" s="3">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1213,8 +1235,11 @@
       <c r="E4" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F4" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1230,8 +1255,11 @@
       <c r="E5" s="3">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F5" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1247,8 +1275,11 @@
       <c r="E6" s="3">
         <v>11.8</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F6" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1264,8 +1295,11 @@
       <c r="E7" s="3">
         <v>12.86</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F7" s="3">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1315,11 @@
       <c r="E8" s="3">
         <v>11.79</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F8" s="3">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1298,8 +1335,11 @@
       <c r="E9" s="3">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F9" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1315,8 +1355,11 @@
       <c r="E10" s="3">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F10" s="3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1332,8 +1375,11 @@
       <c r="E11" s="3">
         <v>13.24</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F11" s="3">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1349,8 +1395,11 @@
       <c r="E12" s="3">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F12" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1366,8 +1415,11 @@
       <c r="E13" s="3">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F13" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1383,8 +1435,11 @@
       <c r="E14" s="3">
         <v>17.489999999999998</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F14" s="3">
+        <v>10.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>91</v>
       </c>
@@ -1400,8 +1455,11 @@
       <c r="E15" s="3">
         <v>0.62</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F15" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1417,8 +1475,11 @@
       <c r="E16" s="3">
         <v>4.7699999999999996</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F16" s="3">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1434,8 +1495,11 @@
       <c r="E17" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F17" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1451,8 +1515,11 @@
       <c r="E18" s="3">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F18" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1468,8 +1535,11 @@
       <c r="E19" s="3">
         <v>12.19</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F19" s="3">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1485,8 +1555,11 @@
       <c r="E20" s="3">
         <v>13.77</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F20" s="3">
+        <v>9.0399999999999991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1502,8 +1575,11 @@
       <c r="E21" s="3">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F21" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1519,8 +1595,11 @@
       <c r="E22" s="3">
         <v>7.58</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F22" s="3">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1536,8 +1615,11 @@
       <c r="E23" s="3">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F23" s="3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1635,11 @@
       <c r="E24" s="3">
         <v>2.2799999999999998</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F24" s="3">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1570,8 +1655,11 @@
       <c r="E25" s="3">
         <v>16.059999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F25" s="3">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1587,8 +1675,11 @@
       <c r="E26" s="3">
         <v>12.09</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F26" s="3">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -1604,8 +1695,11 @@
       <c r="E27" s="3">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F27" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1621,8 +1715,11 @@
       <c r="E28" s="3">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F28" s="3">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1638,8 +1735,11 @@
       <c r="E29" s="3">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F29" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -1655,8 +1755,11 @@
       <c r="E30" s="3">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F30" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -1672,8 +1775,11 @@
       <c r="E31" s="3">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F31" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1795,11 @@
       <c r="E32" s="3">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F32" s="3">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1706,8 +1815,11 @@
       <c r="E33" s="3">
         <v>0.31</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F33" s="3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1723,8 +1835,11 @@
       <c r="E34" s="3">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F34" s="3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -1740,8 +1855,11 @@
       <c r="E35" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F35" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -1757,8 +1875,11 @@
       <c r="E36" s="3">
         <v>12.28</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F36" s="3">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1774,8 +1895,11 @@
       <c r="E37" s="3">
         <v>3.99</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F37" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -1791,8 +1915,11 @@
       <c r="E38" s="3">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F38" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -1808,8 +1935,11 @@
       <c r="E39" s="3">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F39" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -1825,8 +1955,11 @@
       <c r="E40" s="3">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F40" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -1842,8 +1975,11 @@
       <c r="E41" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F41" s="3">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1859,8 +1995,11 @@
       <c r="E42" s="3">
         <v>1.34</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F42" s="3">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1876,8 +2015,11 @@
       <c r="E43" s="3">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F43" s="3">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1893,8 +2035,11 @@
       <c r="E44" s="3">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F44" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1910,8 +2055,11 @@
       <c r="E45" s="3">
         <v>0.73</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F45" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>119</v>
       </c>
@@ -1927,8 +2075,11 @@
       <c r="E46" s="3">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F46" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -1944,8 +2095,11 @@
       <c r="E47" s="3">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F47" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1961,8 +2115,11 @@
       <c r="E48" s="3">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F48" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -1978,8 +2135,11 @@
       <c r="E49" s="3">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F49" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1995,8 +2155,11 @@
       <c r="E50" s="3">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F50" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -2012,8 +2175,11 @@
       <c r="E51" s="3">
         <v>0.55000000000000004</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F51" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>118</v>
       </c>
@@ -2029,8 +2195,11 @@
       <c r="E52" s="3">
         <v>12.44</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F52" s="3">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -2046,8 +2215,11 @@
       <c r="E53" s="3">
         <v>34.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F53" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -2063,8 +2235,11 @@
       <c r="E54" s="3">
         <v>4.9800000000000004</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F54" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2080,8 +2255,11 @@
       <c r="E55" s="3">
         <v>0.34</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F55" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -2097,8 +2275,11 @@
       <c r="E56" s="3">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F56" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="4" t="s">
         <v>57</v>
       </c>
@@ -2114,8 +2295,11 @@
       <c r="E57" s="3">
         <v>14.05</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F57" s="3">
+        <v>71.849999999999994</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -2131,8 +2315,11 @@
       <c r="E58" s="3">
         <v>18.22</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F58" s="3">
+        <v>73.53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -2148,8 +2335,11 @@
       <c r="E59" s="3">
         <v>32.049999999999997</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F59" s="3">
+        <v>61.66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -2165,8 +2355,11 @@
       <c r="E60" s="3">
         <v>8.52</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F60" s="3">
+        <v>83.92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2182,8 +2375,11 @@
       <c r="E61" s="3">
         <v>10.92</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F61" s="3">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -2199,8 +2395,11 @@
       <c r="E62" s="3">
         <v>15.77</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F62" s="3">
+        <v>77.31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -2216,8 +2415,11 @@
       <c r="E63" s="3">
         <v>13.46</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F63" s="3">
+        <v>62.85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -2233,8 +2435,11 @@
       <c r="E64" s="3">
         <v>15.85</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F64" s="3">
+        <v>72.08</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -2250,8 +2455,11 @@
       <c r="E65" s="3">
         <v>9.2899999999999991</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F65" s="3">
+        <v>80.86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -2267,8 +2475,11 @@
       <c r="E66" s="3">
         <v>13.82</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F66" s="3">
+        <v>83.57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -2284,8 +2495,11 @@
       <c r="E67" s="3">
         <v>10.16</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F67" s="3">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -2301,8 +2515,11 @@
       <c r="E68" s="3">
         <v>15.69</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F68" s="3">
+        <v>66.13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="4" t="s">
         <v>69</v>
       </c>
@@ -2318,8 +2535,11 @@
       <c r="E69" s="3">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F69" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>120</v>
       </c>
@@ -2335,8 +2555,11 @@
       <c r="E70" s="3">
         <v>1.54</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F70" s="3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -2352,8 +2575,11 @@
       <c r="E71" s="3">
         <v>1.76</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F71" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -2369,8 +2595,11 @@
       <c r="E72" s="3">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F72" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -2386,8 +2615,11 @@
       <c r="E73" s="3">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F73" s="3">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>89</v>
       </c>
@@ -2403,8 +2635,11 @@
       <c r="E74" s="3">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F74" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>72</v>
       </c>
@@ -2420,8 +2655,11 @@
       <c r="E75" s="3">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F75" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>73</v>
       </c>
@@ -2437,8 +2675,11 @@
       <c r="E76" s="3">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F76" s="3">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -2454,8 +2695,11 @@
       <c r="E77" s="3">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F77" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>74</v>
       </c>
@@ -2471,8 +2715,11 @@
       <c r="E78" s="3">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F78" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>75</v>
       </c>
@@ -2488,8 +2735,11 @@
       <c r="E79" s="3">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F79" s="3">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>76</v>
       </c>
@@ -2505,8 +2755,11 @@
       <c r="E80" s="3">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F80" s="3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="4" t="s">
         <v>77</v>
       </c>
@@ -2522,8 +2775,11 @@
       <c r="E81" s="3">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F81" s="3">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>87</v>
       </c>
@@ -2539,8 +2795,11 @@
       <c r="E82" s="3">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F82" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>78</v>
       </c>
@@ -2556,8 +2815,11 @@
       <c r="E83" s="3">
         <v>1.08</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F83" s="3">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -2573,8 +2835,11 @@
       <c r="E84" s="3">
         <v>1.19</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F84" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>79</v>
       </c>
@@ -2590,8 +2855,11 @@
       <c r="E85" s="3">
         <v>1.45</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F85" s="3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>92</v>
       </c>
@@ -2607,8 +2875,11 @@
       <c r="E86" s="3">
         <v>0.71</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F86" s="3">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>80</v>
       </c>
@@ -2624,8 +2895,11 @@
       <c r="E87" s="3">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F87" s="3">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>81</v>
       </c>
@@ -2641,8 +2915,11 @@
       <c r="E88" s="3">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F88" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>82</v>
       </c>
@@ -2658,8 +2935,11 @@
       <c r="E89" s="3">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F89" s="3">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>100</v>
       </c>
@@ -2675,8 +2955,11 @@
       <c r="E90" s="3">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F90" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="4" t="s">
         <v>83</v>
       </c>
@@ -2692,8 +2975,11 @@
       <c r="E91" s="3">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F91" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>88</v>
       </c>
@@ -2709,8 +2995,11 @@
       <c r="E92" s="3">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F92" s="3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -2726,8 +3015,11 @@
       <c r="E93" s="3">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2743,8 +3035,11 @@
       <c r="E94" s="3">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F94" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2760,8 +3055,11 @@
       <c r="E95" s="3">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F95" s="3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2777,8 +3075,11 @@
       <c r="E96" s="3">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F96" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2794,8 +3095,11 @@
       <c r="E97" s="3">
         <v>0.19</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F97" s="3">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2811,8 +3115,11 @@
       <c r="E98" s="3">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F98" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2828,8 +3135,11 @@
       <c r="E99" s="3">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F99" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -2845,18 +3155,28 @@
       <c r="E100" s="3">
         <v>0.17</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F100" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="F101" s="3"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
-      <c r="G102" t="s">
+      <c r="F102" s="3"/>
+      <c r="H102" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="F103" s="3"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -2872,11 +3192,14 @@
       <c r="E104" s="10">
         <v>0.05</v>
       </c>
-      <c r="G104" s="9" t="s">
+      <c r="F104" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="H104" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>41</v>
       </c>
@@ -2892,11 +3215,14 @@
       <c r="E105" s="10">
         <v>0.49</v>
       </c>
-      <c r="G105" s="9" t="s">
+      <c r="F105" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>58</v>
       </c>
@@ -2912,11 +3238,14 @@
       <c r="E106" s="10">
         <v>10.65</v>
       </c>
-      <c r="G106" s="9" t="s">
+      <c r="F106" s="3">
+        <v>80.03</v>
+      </c>
+      <c r="H106" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>52</v>
       </c>
@@ -2932,11 +3261,14 @@
       <c r="E107" s="10">
         <v>8.6300000000000008</v>
       </c>
-      <c r="G107" s="9" t="s">
+      <c r="F107" s="3">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>46</v>
       </c>
@@ -2952,11 +3284,14 @@
       <c r="E108" s="3">
         <v>4.2</v>
       </c>
-      <c r="G108" s="9" t="s">
+      <c r="F108" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="H108" s="9" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>70</v>
       </c>
@@ -2972,11 +3307,17 @@
       <c r="E109" s="3">
         <v>1.54</v>
       </c>
-      <c r="G109" s="9" t="s">
+      <c r="F109" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="F110" s="3"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>121</v>
       </c>
@@ -2992,11 +3333,14 @@
       <c r="E111" s="3">
         <v>0.71</v>
       </c>
-      <c r="G111" t="s">
+      <c r="F111" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="H111" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>122</v>
       </c>
@@ -3012,11 +3356,14 @@
       <c r="E112" s="3">
         <v>0.84</v>
       </c>
-      <c r="G112" t="s">
+      <c r="F112" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="H112" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>123</v>
       </c>
@@ -3032,11 +3379,17 @@
       <c r="E113" s="10">
         <v>14.35</v>
       </c>
-      <c r="G113" t="s">
+      <c r="F113" s="3">
+        <v>64.16</v>
+      </c>
+      <c r="H113" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="F114" s="3"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>156</v>
       </c>
@@ -3052,11 +3405,14 @@
       <c r="E115" s="3">
         <v>0.84</v>
       </c>
-      <c r="G115" t="s">
+      <c r="F115" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="H115" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>157</v>
       </c>
@@ -3072,7 +3428,10 @@
       <c r="E116" s="3">
         <v>0.71</v>
       </c>
-      <c r="G116" t="s">
+      <c r="F116" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="H116" t="s">
         <v>159</v>
       </c>
     </row>
